--- a/public/assets/download/product_bulk_import_sample.xlsx
+++ b/public/assets/download/product_bulk_import_sample.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\devel\laravel\XFX-Force\public\assets\download\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomsh\Laravel\XFX-Force\public\assets\download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{820320AC-EC04-4C3E-9A6B-7E3FD3AB03CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344570AA-F19F-43E4-A56A-EFE2CAD3A0C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{12C5A337-4CB1-4358-9DE4-337E8EB8E5BF}"/>
   </bookViews>
@@ -170,9 +170,6 @@
     <t>WARRANTY 2 DESCRIPTION</t>
   </si>
   <si>
-    <t>MATA TITLE</t>
-  </si>
-  <si>
     <t>META DESCRIPTION</t>
   </si>
   <si>
@@ -393,6 +390,9 @@
   </si>
   <si>
     <t>Product 002 - updated</t>
+  </si>
+  <si>
+    <t>META TITLE</t>
   </si>
 </sst>
 </file>
@@ -965,25 +965,25 @@
         <v>43</v>
       </c>
       <c r="AS1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AY1" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="AY1" s="2" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:51" x14ac:dyDescent="0.3">
@@ -992,28 +992,28 @@
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="F2" s="3">
         <v>5</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="K2" s="3">
         <v>20</v>
@@ -1028,13 +1028,13 @@
         <v>44</v>
       </c>
       <c r="O2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q2" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="R2" s="4">
         <v>46066</v>
@@ -1046,23 +1046,23 @@
         <v>12</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="W2" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="X2" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="X2" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA2" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="AB2" s="3">
         <v>4</v>
@@ -1071,28 +1071,28 @@
         <v>1200</v>
       </c>
       <c r="AD2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE2" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AE2" s="3" t="s">
+      <c r="AF2" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="AF2" s="3" t="s">
+      <c r="AG2" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AG2" s="3" t="s">
+      <c r="AH2" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="AH2" s="3" t="s">
+      <c r="AI2" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="AI2" s="3" t="s">
+      <c r="AJ2" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="AJ2" s="3" t="s">
+      <c r="AK2" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="AK2" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="AL2" s="3">
         <v>49</v>
@@ -1101,10 +1101,10 @@
         <v>12</v>
       </c>
       <c r="AN2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AO2" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="AO2" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="AP2" s="3">
         <v>79</v>
@@ -1113,28 +1113,28 @@
         <v>24</v>
       </c>
       <c r="AR2" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AS2" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="AT2" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="AT2" s="6" t="s">
+      <c r="AU2" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AU2" s="6" t="s">
+      <c r="AV2" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="AV2" s="6" t="s">
+      <c r="AW2" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="AW2" s="6" t="s">
+      <c r="AX2" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="AX2" s="6" t="s">
+      <c r="AY2" s="6" t="s">
         <v>107</v>
-      </c>
-      <c r="AY2" s="6" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:51" x14ac:dyDescent="0.3">
@@ -1145,28 +1145,28 @@
         <v>1002</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="F3" s="3">
         <v>2</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="J3" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K3" s="3">
         <v>12</v>
@@ -1181,13 +1181,13 @@
         <v>20</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R3" s="4">
         <v>46066</v>
@@ -1199,25 +1199,25 @@
         <v>2</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="W3" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y3" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="X3" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y3" s="3" t="s">
+      <c r="Z3" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="Z3" s="3" t="s">
+      <c r="AA3" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="AA3" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="AB3" s="3">
         <v>2</v>
@@ -1226,28 +1226,28 @@
         <v>500</v>
       </c>
       <c r="AD3" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE3" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="AE3" s="3" t="s">
+      <c r="AF3" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="AF3" s="3" t="s">
+      <c r="AG3" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="AG3" s="3" t="s">
+      <c r="AH3" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="AH3" s="3" t="s">
+      <c r="AI3" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="AI3" s="3" t="s">
+      <c r="AJ3" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AJ3" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="AK3" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AL3" s="3">
         <v>80</v>
@@ -1256,10 +1256,10 @@
         <v>18</v>
       </c>
       <c r="AN3" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AO3" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AP3" s="3">
         <v>109</v>
@@ -1268,28 +1268,28 @@
         <v>36</v>
       </c>
       <c r="AR3" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AS3" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AT3" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="AT3" s="6" t="s">
+      <c r="AU3" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="AU3" s="6" t="s">
+      <c r="AV3" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="AV3" s="6" t="s">
+      <c r="AW3" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="AW3" s="6" t="s">
+      <c r="AX3" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="AX3" s="6" t="s">
+      <c r="AY3" s="6" t="s">
         <v>114</v>
-      </c>
-      <c r="AY3" s="6" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:51" x14ac:dyDescent="0.3">
@@ -1300,28 +1300,28 @@
         <v>1002</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D4" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="F4" s="3">
         <v>2</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K4" s="3">
         <v>12</v>
@@ -1336,13 +1336,13 @@
         <v>20</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R4" s="4">
         <v>46066</v>
@@ -1354,25 +1354,25 @@
         <v>1</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="W4" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y4" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="X4" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y4" s="3" t="s">
+      <c r="Z4" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="Z4" s="3" t="s">
+      <c r="AA4" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="AA4" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="AB4" s="3">
         <v>5</v>
@@ -1381,28 +1381,28 @@
         <v>300</v>
       </c>
       <c r="AD4" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AE4" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="AE4" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="AF4" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AG4" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="AG4" s="3" t="s">
+      <c r="AH4" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="AH4" s="3" t="s">
+      <c r="AI4" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="AI4" s="3" t="s">
+      <c r="AJ4" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AJ4" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="AK4" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AL4" s="3">
         <v>80</v>
@@ -1411,10 +1411,10 @@
         <v>18</v>
       </c>
       <c r="AN4" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AO4" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AP4" s="3">
         <v>109</v>
@@ -1423,7 +1423,7 @@
         <v>36</v>
       </c>
       <c r="AR4" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AS4" s="3"/>
       <c r="AT4" s="3"/>
